--- a/光伏配储项目/电价数据/2026/渡水站.xlsx
+++ b/光伏配储项目/电价数据/2026/渡水站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.49365</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38446</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7323999999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5549500000000001</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5772999999999999</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.49309</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.46468</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43538</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45183</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.42703</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.41994</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41676</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.4069</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39596</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39551</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38352</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.39949</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42072</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41058</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35346</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.38995</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38356</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41521</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39065</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.41889</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41221</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42212</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41059</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.4406600000000001</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.49225</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.39627</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31113</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.36639</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.08952</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.09759000000000001</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.21367</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.10853</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.07487000000000001</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.01041</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.07843000000000001</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.27929</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.2818</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14214</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.2141</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.2224</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.22513</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.2119</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.18712</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.11579</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.23188</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.24857</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.28669</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.23812</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.11251</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.3765</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.48606</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.5365599999999999</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.72973</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.1309</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39389</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.21711</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.42995</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43657</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.6585</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.8715900000000001</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.47941</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.20424</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.18927</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.11566</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.2858</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.23545</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.44529</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.68952</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.7383099999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.97653</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.91453</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.89298</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.79791</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.75789</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5095299999999999</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48109</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.45826</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41649</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42624</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.71141</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8865499999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.93635</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49995</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51893</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5055500000000001</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50563</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48794</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40062</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46975</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37897</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38032</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39712</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35714</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.38017</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37787</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36265</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38228</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.986</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.8326699999999999</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.93033</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.47035</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.45998</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38235</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38165</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.41854</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5073</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.32121</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35604</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.26382</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.30097</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29648</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.36582</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.47168</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.7346200000000001</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.9431799999999999</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.32556</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.45571</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.77251</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.7480399999999999</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.42579</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.6842999999999999</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.26045</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.88835</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.8704</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.29656</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.35229</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.42177</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.52199</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.47206</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.47694</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.72288</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.56702</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.71373</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.7097599999999999</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.14633</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.15941</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.09541</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.81445</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.19202</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.09529</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.25105</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.01716</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.07907</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.6441399999999999</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.9716399999999999</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.91018</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.9372699999999999</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.72601</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.9259500000000001</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.7661</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.76641</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.44871</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.76422</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.80133</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44962</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42856</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44351</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37607</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35497</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33474</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50971</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.49123</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48338</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.43742</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41241</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36681</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39027</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38345</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36367</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42897</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44463</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37097</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39691</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36758</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36841</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.3564</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36197</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36925</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38621</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39702</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47455</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44458</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43907</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39499</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35323</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36699</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.19751</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.21124</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.16088</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.27187</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.14133</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.18982</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.25004</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30788</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.30234</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.49333</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.42098</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.69568</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.30648</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.5205</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.65718</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.75342</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.466</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.43914</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.75425</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.53512</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.5696100000000001</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.5435800000000001</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.48482</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.38642</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.37312</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.40376</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.48304</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.48167</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.56552</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.58631</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.5143799999999999</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.53196</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.26538</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.61754</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.46558</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5049399999999999</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.5096700000000001</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.58894</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.53725</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.6624099999999999</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.4401600000000001</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.4166</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.47061</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.61258</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.61488</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.56031</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.7366900000000001</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.6236699999999999</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.54364</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.45755</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.5918099999999999</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.42599</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45706</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39717</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.3616</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34212</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.50325</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.50358</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.43038</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39386</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39224</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39945</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37003</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36175</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.39377</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.39109</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36764</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.4497</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36478</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36166</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.3633</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35192</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33934</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38999</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38941</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35402</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37983</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34621</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.3974</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42169</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.43075</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.39573</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.20269</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.12878</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.26504</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.12275</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.29881</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.51018</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.03929</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.33669</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.24703</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.13365</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.07148</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.28917</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35846</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.28227</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.37646</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.62233</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.27505</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.30836</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.46271</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.39777</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.40805</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.2765</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.28935</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.29468</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.46625</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.44277</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.5047200000000001</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45183</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46431</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40202</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.4752</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.50957</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.55864</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.42859</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.54757</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.48966</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.46004</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50761</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.41736</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.39765</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.3957</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.42193</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32316</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31575</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.29806</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38201</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36086</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32641</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31663</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31508</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.30912</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31455</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31501</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30764</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30714</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31408</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.27124</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.28504</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.28878</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.26446</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.28472</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.27917</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.23878</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30385</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.24403</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.12629</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.2513</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.18146</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.14428</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.11873</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.21637</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.02029</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.21561</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.21338</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.19672</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04668</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.02571</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.00107</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22132</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.15371</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.15916</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.06085</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.04843</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00561</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.22531</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29606</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29873</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.2962</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30278</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33627</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.39353</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39732</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.39317</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.38007</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.36133</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40538</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.40427</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41469</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.47076</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37682</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39956</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.4040899999999999</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.50874</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35636</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34494</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35448</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36853</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.68868</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.41049</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.46751</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.44161</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.44392</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.3635</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.3663</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.36048</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.3420299999999999</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.36667</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.39726</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33813</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30382</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.35715</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10245</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04336</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04501</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.23367</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.00304</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.1813</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.03686</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.23867</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.12368</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.03069</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04391</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04393</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04573</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04559000000000001</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04334</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04548</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04338</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.02422</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04531</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04537</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04357</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.03545</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.03357</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04986</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04792</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19974</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29464</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29981</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29491</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29327</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.2938</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36918</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33747</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33322</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31831</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40906</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35226</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29443</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15944</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26884</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27065</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29719</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38155</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42827</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45651</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.4184</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41523</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38955</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40238</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29928</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15655</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.2942</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31092</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31341</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31261</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38544</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62203</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78535</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78101</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92038</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49455</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9141699999999999</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86283</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29616</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88742</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63158</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18701</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8694</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5922000000000001</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33077</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03286</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53071</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909299999999999</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.54469</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77291</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87676</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87383</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.4931</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39862</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39982</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44988</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20692</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87882</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55101</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62178</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5383</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49767</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.4558</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42424</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43713</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45002</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38815</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41981</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40068</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.3664</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38568</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41753</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43739</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39177</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34725</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.41183</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45146</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35708</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40385</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40813</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.6001299999999999</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.44608</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.60139</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.74885</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.88167</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46868</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.4314</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5952999999999999</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.4591</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.90666</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.6591</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8572799999999999</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87507</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.45363</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.7320599999999999</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.30186</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.67241</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.57637</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33395</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.4065</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31914</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34812</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31413</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30481</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29606</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31266</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31562</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32699</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32973</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35743</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34565</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34337</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.42128</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.42417</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.46737</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.42674</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.40056</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.38388</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35657</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.92214</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.41637</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.41831</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.48138</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38827</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41999</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36607</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.37169</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.35427</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33373</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.36467</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.41151</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.5194099999999999</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.36265</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.39716</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34832</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.36132</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37833</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.3641</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36937</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.32071</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31597</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.35413</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29148</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31075</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.27869</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.29486</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.15296</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30387</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30867</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.30149</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27188</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19929</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29918</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32322</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28225</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31213</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31256</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35369</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.36483</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31684</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31582</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.31689</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.36365</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.31633</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31709</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29877</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.31256</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29047</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.35338</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25619</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32632</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.34311</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.34166</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27707</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35699</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31376</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.39351</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.35565</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.45944</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35543</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42407</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.45433</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34461</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.43009</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.36246</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.41217</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.4114</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.62851</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.36417</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.90023</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.43232</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.16932</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7056</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79669</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.65783</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.61899</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.47588</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45531</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50583</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.44469</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.44823</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41977</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41721</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.43333</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5205700000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41714</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43859</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.42541</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43859</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39399</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.44304</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.46777</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42757</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.44946</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41713</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41645</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.41217</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.4389</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.4029</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.41524</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.4993</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36624</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.36544</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.30033</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.37767</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30889</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30608</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.56153</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.36684</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25002</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.14422</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27898</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.04502</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30113</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26228</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25606</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30651</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28298</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28363</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.28781</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29305</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31797</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34571</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.41144</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40872</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35405</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36408</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34352</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.34281</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.3721</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.37128</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.37051</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36603</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.3527</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5845499999999999</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.47747</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.88088</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.48044</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.44972</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.38389</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.45824</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.39332</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37486</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.33165</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.43886</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34782</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.35787</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.34301</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32237</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31324</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31388</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.41204</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.36287</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.36527</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4213</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.39492</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.36694</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.35345</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.30385</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.28433</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.29974</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29565</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22212</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.13388</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14826</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28381</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15984</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.13743</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.1409</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.2646</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.24507</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14279</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25733</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.28685</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.16752</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.11333</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.10541</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.12277</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.11885</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.19782</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.13676</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28071</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34361</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.36419</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.36284</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.35584</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34776</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38748</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.35137</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40835</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36737</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.39388</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.46555</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.4104</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.41234</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.40713</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.46807</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.45475</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.45348</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.45869</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44701</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40554</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39351</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.40054</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39435</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.3669</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36727</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.35569</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.34415</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5624400000000001</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.39175</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.48518</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.43558</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.42705</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37774</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38936</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38757</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.40174</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38262</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37317</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38792</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36594</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.40008</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.3773</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38915</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35597</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.46608</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.3782799999999999</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38893</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36661</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.33153</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35329</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36463</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29935</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29604</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27072</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.25123</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.1649</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.31139</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.23091</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.23806</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.25647</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30112</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.33449</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31319</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.27659</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.27992</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24448</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.3066</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.4521</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.36321</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.38599</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35403</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.41798</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.38724</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.36175</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.25699</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.38409</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38478</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35901</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.36201</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.42105</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35343</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.37078</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37489</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36356</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.39005</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38812</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.39316</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35466</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.366</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34213</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.37194</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.52564</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37361</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.53639</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38753</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.37867</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36691</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35839</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.35323</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35471</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34725</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34674</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.34141</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.3454100000000001</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.3885</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.37733</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.38117</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.38611</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.38223</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.45157</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.05033</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.42674</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.63085</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.50925</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.48525</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.44845</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.40834</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.30933</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.37073</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.29884</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.49339</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.26262</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.18892</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.03607</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.23999</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.35429</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.19591</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.26787</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.28479</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.28204</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.29385</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.2924</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.29029</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.42442</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.3512</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.28546</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.27796</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.41349</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.3015</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34394</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.29781</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35712</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.40334</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32765</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.49438</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.4555</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.29509</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.43838</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.41977</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.69338</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36478</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.80672</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.71887</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.59402</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.37772</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5121</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.25151</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.38448</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.34313</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.37819</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.3464</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.44139</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.40267</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.35349</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.37616</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.35723</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.33283</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.34492</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.33434</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.34412</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32959</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.36608</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.36988</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.35352</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.36452</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.35884</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.38312</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.38273</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33797</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.2845299999999999</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.38726</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.35122</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28669</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.34565</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.30676</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.27918</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.21288</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.30151</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36628</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34734</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.35793</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35389</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.37733</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33743</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.38919</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.37594</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36786</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.38059</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36904</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36677</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.40928</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.39591</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37486</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.4224</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.39062</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.3752200000000001</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.37726</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.3532</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.36142</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.3528</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.34452</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35352</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35449</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.35666</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.39938</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37831</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.34412</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34272</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.34205</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.34132</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.35573</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.35578</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34643</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.35533</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37121</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.28743</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.23408</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.31715</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.31315</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.31709</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.36286</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35712</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.36278</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36415</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36342</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36392</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35187</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38801</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.38678</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38737</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.39091</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.44135</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41439</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38564</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37895</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6595800000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.81637</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.46444</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.29672</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.47211</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.36636</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.3535</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.34274</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34943</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41433</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37607</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36525</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.36206</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36523</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.36129</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36515</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.36218</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35604</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36548</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35528</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.36444</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.36301</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.38008</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.36198</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35972</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36327</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36327</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38656</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36908</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38308</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35439</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35293</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33221</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.34842</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.34559</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.27019</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.15483</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28178</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.26925</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.18892</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.2627</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.30357</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.30516</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27555</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.20651</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.24973</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28033</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27216</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.2995</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.28883</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30436</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.38591</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.28015</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.30034</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.30145</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.35199</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.32541</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.37872</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.38285</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.39741</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.47381</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.44008</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.45377</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.66653</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6237200000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.64185</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.5352100000000001</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.83831</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.5205299999999999</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.53167</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.50888</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.4205</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.40724</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.39838</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.50731</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.44304</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.4304</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.38498</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37808</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.37282</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36515</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.50642</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.60261</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.5337999999999999</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.72548</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42706</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.42781</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.41155</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.42004</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41725</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.42668</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40705</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39774</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41866</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41648</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.40133</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.39118</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.43074</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.42845</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39909</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.41218</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.41045</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.42381</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.41113</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.46909</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.46586</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.58997</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.5220199999999999</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.4662</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.51288</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.46364</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.42307</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.36566</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.40253</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.39327</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.48332</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.43776</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.3861</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.36975</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.4051</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.39816</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.40502</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.2867</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.30769</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.38625</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.58858</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.29556</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.35222</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.33225</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.30731</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33721</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.34968</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37929</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.36272</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.37873</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.38274</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.39276</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.39227</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.42227</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.44838</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.51034</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.46388</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.53691</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.5368999999999999</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.5833400000000001</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.74749</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.8989400000000001</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.01952</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.7607999999999999</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.71446</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.54028</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.88573</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6264</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6752100000000001</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.44342</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.48317</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.50016</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.49361</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.48616</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.42741</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.57602</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.43929</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.45469</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.4704700000000001</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43741</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42738</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.45948</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41909</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40825</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.47522</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.40935</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.41675</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.39433</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.38471</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.38027</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36321</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36899</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.41668</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.3813</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36823</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36287</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36899</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.40158</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.38252</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.37421</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36439</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.38255</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40121</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.3773</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.39067</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.40281</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.40332</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38986</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.37486</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34848</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.14125</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.38027</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.31384</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.35573</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.35407</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.39747</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35608</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.46272</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.3929</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46794</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.3117</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31743</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.09029000000000001</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.17711</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.31091</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.39878</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.40395</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.37513</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.42752</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.38756</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43637</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.42051</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.46128</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.42162</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.40419</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.4104</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.42805</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.42455</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.38741</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37941</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.40987</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36322</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.3884</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.36477</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.41172</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.40271</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.3836</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.38064</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.41782</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.40217</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.38268</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.34473</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.52124</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.41775</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.41088</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.39628</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.3699</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.4194</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.36685</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.39776</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.39394</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.36972</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.39945</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.36174</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.36892</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.37692</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.35559</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.35408</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.36458</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.36649</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.36982</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.36525</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.36796</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.39086</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31408</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.24784</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.22142</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.29161</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24228</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.24029</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.16455</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.33193</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.24762</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04787</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.29309</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.27729</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.15542</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.171</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.30511</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31317</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30903</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22494</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.25228</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26417</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23155</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27672</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28551</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.2911</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.34238</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.35386</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35592</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.38312</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35939</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.37239</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.39056</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.4044700000000001</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.35774</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.38531</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.36699</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.3912</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.36508</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39115</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.41258</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.35343</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.38683</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34929</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.38835</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.40086</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35735</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.36707</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.3552</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.36736</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.36244</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.34769</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.36363</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.33748</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.34199</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.31636</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.23836</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.28138</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.28638</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.02054</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.15068</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02419</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03961</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01523</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.0433</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04129</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04868</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04835</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02445</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.0297</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.02614</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04943</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00115</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.28188</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04968</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04931</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03534</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01603</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04969</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03548</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20632</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.27081</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29337</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.2798</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.34936</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.34726</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.35756</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.37215</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.36381</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.36826</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.35607</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.36483</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.39211</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.37262</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.39571</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.36855</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.36764</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.36447</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.37072</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.35643</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.37348</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.93864</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.83784</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.44142</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.60678</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.45423</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.47121</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.51251</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.39923</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.40986</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.37794</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.38462</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.42925</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.37187</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.35193</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.44638</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.36865</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.42771</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.39539</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.43564</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.40175</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.41217</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.4308999999999999</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.45856</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.45335</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.43144</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.37355</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.36202</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.39561</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.44001</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.01198</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.06981</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.90339</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8926900000000001</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.40495</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.16114</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.3514</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.29014</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.3147799999999999</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.37593</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.4904</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.9326100000000001</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.31184</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00583</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.30641</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00385</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.0746</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.31287</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.32373</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25419</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29172</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47673</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.3948</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.41001</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.38444</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.3732</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.41153</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.79567</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.88285</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.9029700000000001</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.89412</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.53315</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.98381</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.89899</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.91091</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.9232400000000001</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.84811</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.84642</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.85042</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.94747</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.89615</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.9193</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.89619</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.38042</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.36973</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.38146</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.3853</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.51755</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.71577</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.9672799999999999</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.67228</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.5043</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.52159</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.44579</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.43945</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.3906</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.41507</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.42149</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.36258</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.35753</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.5097699999999999</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.36786</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.37338</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.3584</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.36302</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.36671</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.40889</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.41296</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.40181</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.41614</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.5160800000000001</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.5453600000000001</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.41237</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.4347200000000001</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.33003</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.35281</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.49083</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.38769</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.54643</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.3884</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.43799</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.46129</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.39207</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.38848</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.37341</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.45449</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30657</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31363</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26093</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31312</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30448</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30447</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.32097</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.34799</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.33064</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32487</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.36114</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34829</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33486</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.37135</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.40709</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.40484</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.39246</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34982</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.38972</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.38727</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.43707</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.53186</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.9352</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.44432</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.72233</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.52146</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.40422</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.47224</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.46466</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.43226</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.55836</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.3766</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.38633</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.36581</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.3716</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.36562</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.45395</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.4621</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.44048</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.43121</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.41399</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.4091</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.40607</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.37749</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.38436</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.37607</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.37669</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35775</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.37314</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.36507</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.3533</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.37592</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.34966</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.35192</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.35294</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.36554</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.37503</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.3757799999999999</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.36463</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.37612</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.46546</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.39627</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.38275</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.68371</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.87983</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.66416</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.46013</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.64073</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.5123</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37699</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36631</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35397</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35417</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.36611</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.36373</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.39647</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.28914</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.32737</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.3454100000000001</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34413</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32548</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32251</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.2953</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.37581</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.37895</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47294</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.5232899999999999</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.80602</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.2877</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.40498</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.45106</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.52803</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.40394</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.80067</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.46211</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.78176</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.66088</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.52251</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.52119</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.40683</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.38374</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41819</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.3704</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.37242</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.36401</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.47114</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40864</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.37518</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.40931</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.38507</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.25456</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37814</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36544</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.3739</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.48617</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40767</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40914</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39923</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36515</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.38208</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37722</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.38494</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.38332</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.3752200000000001</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.37158</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36584</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36412</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.36528</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36502</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35346</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36756</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37714</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40932</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.38242</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36859</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36237</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36668</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.39142</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.38995</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.3762200000000001</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43325</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37855</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37346</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.37479</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.36622</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.3102200000000001</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36354</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.24305</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.37763</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29271</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.30012</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.30277</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34391</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33314</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34398</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.38627</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.37806</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.38299</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.38931</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.4152</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.38564</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.3947</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.4293</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.42993</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.47868</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.55515</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.49724</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.42432</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.7337899999999999</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.62424</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.4964</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.49471</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.6808500000000001</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.48252</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.69989</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.79461</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.85211</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.78288</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.72217</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.87779</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.40062</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44168</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.40133</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37849</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.38187</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37231</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37814</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.30744</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.37404</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.37371</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37187</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.36349</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35356</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.36809</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.35392</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35621</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.40884</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.35636</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.34474</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.36576</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.36201</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.39482</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.35427</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.35283</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.35796</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.38197</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.3742</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.38847</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.39152</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.36948</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.36724</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.36466</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.40158</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.34817</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.3719</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.35566</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.33217</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.10682</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.23028</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.27525</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.13753</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.28597</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.08047</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.17664</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.15761</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.28129</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.25185</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.12885</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.39808</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>-0.03112</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.02207</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.18652</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.0384</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.27963</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.18972</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.12847</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.16372</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.30142</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.3746</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.35859</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36241</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.37659</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.38044</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.36423</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.38613</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.4324</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.40668</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.38518</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.47846</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.44119</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.38914</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.41025</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.38527</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.36691</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.42115</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37405</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.43757</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38656</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37851</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.36234</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.36498</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.3888</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.06235</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.38058</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.5053</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.49481</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.38888</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.38635</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.4285</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.39894</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.40842</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.3915</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.39001</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38581</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.38337</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.39146</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38759</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38946</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.38846</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.38238</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.37922</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.38218</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.38087</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.38078</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.37627</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.36996</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38045</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.37196</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.3748</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.36854</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.37262</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.38101</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.38015</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.37199</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.35103</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.38515</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.37021</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.19828</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.29347</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.29135</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.30036</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.25245</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.24183</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.25416</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.24115</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.26874</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.17148</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.23531</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.22083</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.38335</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.22678</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.28643</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.34558</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35368</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.3555</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.35436</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.39983</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.39223</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.43235</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41579</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.41109</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.3647</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37612</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39324</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.38538</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.35558</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.40102</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.38697</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38527</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.39929</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37787</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.40106</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.33315</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.37127</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.3976</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.36757</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.37832</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.37071</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.3708</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.37224</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.45883</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39801</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.40545</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37459</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.38955</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.38877</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.38541</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.38895</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.38873</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.3866</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37787</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.37603</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.37956</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.37492</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.35816</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.37629</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.37739</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.3774</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.37325</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.37154</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.37004</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.37093</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.37348</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.36699</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.35207</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.3732200000000001</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.36553</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.36644</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17814</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.29876</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29942</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14772</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.20153</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14398</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.26944</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.05021</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.10579</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.30874</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.19862</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.20715</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.11558</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.13692</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.23951</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.15718</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.26453</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.23027</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26912</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15671</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.36987</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.16916</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.2306</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.32182</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20168</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14719</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.28748</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.24704</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.29125</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.36339</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.36202</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.39157</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.35961</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.36552</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.39236</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.38604</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.38686</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.39332</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35635</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.40837</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.3968</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.38406</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.41092</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.48291</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39577</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39314</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.39307</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.3962</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.3735</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38955</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.3953</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.39604</v>
       </c>
     </row>
   </sheetData>
